--- a/PM teori/Excel App/Project_Controlling_App.xlsx
+++ b/PM teori/Excel App/Project_Controlling_App.xlsx
@@ -225,6 +225,36 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Segoe UI"/>
+        <b val="1"/>
+        <color rgb="0078281F"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FADBD8"/>
+          <bgColor rgb="00FADBD8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Segoe UI"/>
+        <b val="1"/>
+        <color rgb="007E5109"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCF3CF"/>
+          <bgColor rgb="00FCF3CF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6928,15 +6958,17 @@
         <f>VLOOKUP(A18, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E18" s="19" t="b">
-        <v>0</v>
+      <c r="E18" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A18, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F18" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A18)</f>
         <v/>
       </c>
-      <c r="G18" s="20" t="b">
-        <v>0</v>
+      <c r="G18" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A18, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H18" s="19">
         <f>D18*G18</f>
@@ -6995,15 +7027,17 @@
         <f>VLOOKUP(A19, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E19" s="19" t="b">
-        <v>0</v>
+      <c r="E19" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A19, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F19" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A19)</f>
         <v/>
       </c>
-      <c r="G19" s="20" t="b">
-        <v>0</v>
+      <c r="G19" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A19, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H19" s="19">
         <f>D19*G19</f>
@@ -7062,15 +7096,17 @@
         <f>VLOOKUP(A20, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E20" s="19" t="b">
-        <v>0</v>
+      <c r="E20" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A20, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F20" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A20)</f>
         <v/>
       </c>
-      <c r="G20" s="20" t="b">
-        <v>0</v>
+      <c r="G20" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A20, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H20" s="19">
         <f>D20*G20</f>
@@ -7129,15 +7165,17 @@
         <f>VLOOKUP(A21, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E21" s="19" t="b">
-        <v>0</v>
+      <c r="E21" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A21, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F21" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A21)</f>
         <v/>
       </c>
-      <c r="G21" s="20" t="b">
-        <v>0</v>
+      <c r="G21" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A21, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H21" s="19">
         <f>D21*G21</f>
@@ -7196,15 +7234,17 @@
         <f>VLOOKUP(A22, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E22" s="19" t="b">
-        <v>0</v>
+      <c r="E22" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A22, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F22" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A22)</f>
         <v/>
       </c>
-      <c r="G22" s="20" t="b">
-        <v>0</v>
+      <c r="G22" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A22, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H22" s="19">
         <f>D22*G22</f>
@@ -7263,15 +7303,17 @@
         <f>VLOOKUP(A23, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E23" s="19" t="b">
-        <v>0</v>
+      <c r="E23" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A23, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F23" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A23)</f>
         <v/>
       </c>
-      <c r="G23" s="20" t="b">
-        <v>0</v>
+      <c r="G23" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A23, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H23" s="19">
         <f>D23*G23</f>
@@ -7330,15 +7372,17 @@
         <f>VLOOKUP(A24, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E24" s="19" t="b">
-        <v>0</v>
+      <c r="E24" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A24, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F24" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A24)</f>
         <v/>
       </c>
-      <c r="G24" s="20" t="b">
-        <v>0</v>
+      <c r="G24" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A24, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H24" s="19">
         <f>D24*G24</f>
@@ -7397,15 +7441,17 @@
         <f>VLOOKUP(A25, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E25" s="19" t="b">
-        <v>0</v>
+      <c r="E25" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A25, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F25" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A25)</f>
         <v/>
       </c>
-      <c r="G25" s="20" t="b">
-        <v>0</v>
+      <c r="G25" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A25, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H25" s="19">
         <f>D25*G25</f>
@@ -7464,15 +7510,17 @@
         <f>VLOOKUP(A26, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E26" s="19" t="b">
-        <v>0</v>
+      <c r="E26" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A26, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F26" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A26)</f>
         <v/>
       </c>
-      <c r="G26" s="20" t="b">
-        <v>0</v>
+      <c r="G26" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A26, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H26" s="19">
         <f>D26*G26</f>
@@ -7531,15 +7579,17 @@
         <f>VLOOKUP(A27, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E27" s="19" t="b">
-        <v>0</v>
+      <c r="E27" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A27, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F27" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A27)</f>
         <v/>
       </c>
-      <c r="G27" s="20" t="b">
-        <v>0</v>
+      <c r="G27" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A27, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H27" s="19">
         <f>D27*G27</f>
@@ -7598,15 +7648,17 @@
         <f>VLOOKUP(A28, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E28" s="19" t="b">
-        <v>0</v>
+      <c r="E28" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A28, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F28" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A28)</f>
         <v/>
       </c>
-      <c r="G28" s="20" t="b">
-        <v>0</v>
+      <c r="G28" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A28, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H28" s="19">
         <f>D28*G28</f>
@@ -7665,15 +7717,17 @@
         <f>VLOOKUP(A29, Dim_WBS!$A:$E, 5, FALSE)</f>
         <v/>
       </c>
-      <c r="E29" s="19" t="b">
-        <v>0</v>
+      <c r="E29" s="19">
+        <f>SUMIFS(Fact_Baseline_PV!$C:$C, Fact_Baseline_PV!$B:$B, A29, Fact_Baseline_PV!$A:$A, "&lt;="&amp;$B$4)</f>
+        <v/>
       </c>
       <c r="F29" s="19">
         <f>SUMIFS(Fact_Actual_Costs!$D:$D, Fact_Actual_Costs!$B:$B, A29)</f>
         <v/>
       </c>
-      <c r="G29" s="20" t="b">
-        <v>0</v>
+      <c r="G29" s="20">
+        <f>IFERROR(_xlfn.MAXIFS(Fact_Physical_Progress!$C:$C, Fact_Physical_Progress!$B:$B, A29, Fact_Physical_Progress!$A:$A, "&lt;="&amp;$B$4), 0)</f>
+        <v/>
       </c>
       <c r="H29" s="19">
         <f>D29*G29</f>
@@ -7859,8 +7913,9 @@
         <f>SUM(E$36:E36)</f>
         <v/>
       </c>
-      <c r="G36" s="31" t="b">
-        <v>0</v>
+      <c r="G36" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B36+4))</f>
+        <v/>
       </c>
       <c r="H36" s="31">
         <f>G36-F36</f>
@@ -7901,8 +7956,9 @@
         <f>SUM(E$36:E37)</f>
         <v/>
       </c>
-      <c r="G37" s="31" t="b">
-        <v>0</v>
+      <c r="G37" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B37+4))</f>
+        <v/>
       </c>
       <c r="H37" s="31">
         <f>G37-F37</f>
@@ -7943,8 +7999,9 @@
         <f>SUM(E$36:E38)</f>
         <v/>
       </c>
-      <c r="G38" s="31" t="b">
-        <v>0</v>
+      <c r="G38" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B38+4))</f>
+        <v/>
       </c>
       <c r="H38" s="31">
         <f>G38-F38</f>
@@ -7985,8 +8042,9 @@
         <f>SUM(E$36:E39)</f>
         <v/>
       </c>
-      <c r="G39" s="31" t="b">
-        <v>0</v>
+      <c r="G39" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B39+4))</f>
+        <v/>
       </c>
       <c r="H39" s="31">
         <f>G39-F39</f>
@@ -8027,8 +8085,9 @@
         <f>SUM(E$36:E40)</f>
         <v/>
       </c>
-      <c r="G40" s="31" t="b">
-        <v>0</v>
+      <c r="G40" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B40+4))</f>
+        <v/>
       </c>
       <c r="H40" s="31">
         <f>G40-F40</f>
@@ -8069,8 +8128,9 @@
         <f>SUM(E$36:E41)</f>
         <v/>
       </c>
-      <c r="G41" s="31" t="b">
-        <v>0</v>
+      <c r="G41" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B41+4))</f>
+        <v/>
       </c>
       <c r="H41" s="31">
         <f>G41-F41</f>
@@ -8111,8 +8171,9 @@
         <f>SUM(E$36:E42)</f>
         <v/>
       </c>
-      <c r="G42" s="31" t="b">
-        <v>0</v>
+      <c r="G42" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B42+4))</f>
+        <v/>
       </c>
       <c r="H42" s="31">
         <f>G42-F42</f>
@@ -8153,8 +8214,9 @@
         <f>SUM(E$36:E43)</f>
         <v/>
       </c>
-      <c r="G43" s="31" t="b">
-        <v>0</v>
+      <c r="G43" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B43+4))</f>
+        <v/>
       </c>
       <c r="H43" s="31">
         <f>G43-F43</f>
@@ -8195,8 +8257,9 @@
         <f>SUM(E$36:E44)</f>
         <v/>
       </c>
-      <c r="G44" s="31" t="b">
-        <v>0</v>
+      <c r="G44" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B44+4))</f>
+        <v/>
       </c>
       <c r="H44" s="31">
         <f>G44-F44</f>
@@ -8237,8 +8300,9 @@
         <f>SUM(E$36:E45)</f>
         <v/>
       </c>
-      <c r="G45" s="31" t="b">
-        <v>0</v>
+      <c r="G45" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B45+4))</f>
+        <v/>
       </c>
       <c r="H45" s="31">
         <f>G45-F45</f>
@@ -8279,8 +8343,9 @@
         <f>SUM(E$36:E46)</f>
         <v/>
       </c>
-      <c r="G46" s="31" t="b">
-        <v>0</v>
+      <c r="G46" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B46+4))</f>
+        <v/>
       </c>
       <c r="H46" s="31">
         <f>G46-F46</f>
@@ -8321,8 +8386,9 @@
         <f>SUM(E$36:E47)</f>
         <v/>
       </c>
-      <c r="G47" s="31" t="b">
-        <v>0</v>
+      <c r="G47" s="31">
+        <f>SUMPRODUCT(Dim_WBS!$E$2:$E$13, SUMIFS(Fact_Physical_Progress!$C$2:$C$100, Fact_Physical_Progress!$B$2:$B$100, Dim_WBS!$A$2:$A$13, Fact_Physical_Progress!$A$2:$A$100, "&lt;="&amp;B47+4))</f>
+        <v/>
       </c>
       <c r="H47" s="31">
         <f>G47-F47</f>
@@ -8370,6 +8436,32 @@
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
+  <conditionalFormatting sqref="P18:P30">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Overrun"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Warning"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K18:K30">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="1">
+      <formula>0.95</formula>
+      <formula>0.9999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18:L30">
+    <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="0">
+      <formula>0.90</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="between" dxfId="1">
+      <formula>0.90</formula>
+      <formula>0.9999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>